--- a/wh.xlsx
+++ b/wh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\whatsappUtility\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D518939C-2857-4467-9C38-AE3F8D590630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6CA3FF-3156-4125-BC98-5978326F22EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C21568DB-D12B-4295-9BBF-05CC606CBA26}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C21568DB-D12B-4295-9BBF-05CC606CBA26}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -420,7 +420,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -458,7 +458,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>919819932674</v>
+        <v>919930937335</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
